--- a/results/01_pollution_assessment/HZD_Toxicity/tables/hzd_benchmark_summary.xlsx
+++ b/results/01_pollution_assessment/HZD_Toxicity/tables/hzd_benchmark_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,26 @@
           <t>benchmark source</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>curve_A</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>curve_k</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TEC_Effect_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PEC_Effect_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -477,6 +497,18 @@
           <t>MacDonald et al. (2000), consensus-based freshwater SQG for Sum DDE</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>26.44551849884827</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1046353581793333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -500,6 +532,18 @@
           <t>MacDonald et al. (2000), consensus-based freshwater SQG for total PCB</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v>25.28436503432457</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.00477838198501532</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -523,6 +567,18 @@
           <t>MacDonald et al. (2000), consensus-based freshwater SQG</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>65.78593959402845</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1268607918641293</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -546,6 +602,18 @@
           <t>MacDonald et al. (2000), consensus-based freshwater SQG</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v>39.44921167580028</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7379546313700351</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -569,6 +637,18 @@
           <t>MacDonald et al. (2000), consensus-based freshwater SQG</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>125.813877128892</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.04355678963263965</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -592,6 +672,18 @@
           <t>MacDonald et al. (2000), consensus-based freshwater SQG</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>41.97103024939027</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.02508040016325758</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -615,6 +707,18 @@
           <t>MacDonald et al. (2000), consensus-based freshwater SQG</t>
         </is>
       </c>
+      <c r="F8" t="n">
+        <v>34.69899029981413</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.345953385416409</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -638,6 +742,18 @@
           <t>MacDonald et al. (2000), consensus-based freshwater SQG</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>250.9079828654766</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1136849026705189</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -661,6 +777,18 @@
           <t>MacDonald et al. (2000), consensus-based freshwater SQG</t>
         </is>
       </c>
+      <c r="F10" t="n">
+        <v>59.60410194238968</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.031935346845623</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -683,6 +811,18 @@
         <is>
           <t>MacDonald et al. (2000), consensus-based freshwater SQG</t>
         </is>
+      </c>
+      <c r="F11" t="n">
+        <v>54.51703863297363</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.00871135792652793</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
